--- a/Resource/GameData/CardDesc_filled_2.xlsx
+++ b/Resource/GameData/CardDesc_filled_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\College_work\Y2\Y2_2026\Y2_Project\Project_Doc\GameData(Excel)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assignment\Y2_2026\Y2_Project\Barathrow4\Resource\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{901573FD-D6B1-4F3C-86C8-A58E510AA598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52F5918-87FA-459E-AC00-BF1107B0C7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5670" yWindow="3075" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -19,16 +19,11 @@
     <sheet name="CardDesc" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="245">
   <si>
     <t>Card</t>
   </si>
@@ -243,9 +238,6 @@
     <t>Charge Attack</t>
   </si>
   <si>
-    <t>atk:7;con:1</t>
-  </si>
-  <si>
     <t>Deal {atk} Damage Consume 1</t>
   </si>
   <si>
@@ -763,6 +755,9 @@
   </si>
   <si>
     <t>Skipped the effected unit upcoming turn</t>
+  </si>
+  <si>
+    <t>gen:3;lag;pre;te</t>
   </si>
 </sst>
 </file>
@@ -808,7 +803,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1024,22 +1019,22 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
-    <col min="2" max="2" width="20.28515625" customWidth="1"/>
-    <col min="7" max="7" width="50.5703125" customWidth="1"/>
-    <col min="8" max="8" width="53.5703125" customWidth="1"/>
-    <col min="10" max="10" width="18.5703125" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="7" max="7" width="50.5546875" customWidth="1"/>
+    <col min="8" max="8" width="53.5546875" customWidth="1"/>
+    <col min="10" max="10" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1062,7 +1057,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1085,7 +1080,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1108,7 +1103,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1131,7 +1126,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1154,7 +1149,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1177,7 +1172,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1200,7 +1195,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -1223,7 +1218,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -1246,7 +1241,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -1269,7 +1264,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -1292,7 +1287,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -1315,12 +1310,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>244</v>
       </c>
       <c r="C14" t="s">
         <v>19</v>
@@ -1338,7 +1333,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -1361,7 +1356,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>55</v>
       </c>
@@ -1384,7 +1379,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>58</v>
       </c>
@@ -1407,7 +1402,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>61</v>
       </c>
@@ -1430,7 +1425,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>64</v>
       </c>
@@ -1453,7 +1448,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -1476,15 +1471,15 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1496,18 +1491,18 @@
         <v>12</v>
       </c>
       <c r="G21" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1519,18 +1514,18 @@
         <v>12</v>
       </c>
       <c r="G22" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1539,44 +1534,44 @@
         <v>40</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D24">
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F24" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="G24" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1585,21 +1580,21 @@
         <v>29</v>
       </c>
       <c r="F25" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="G25" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1608,21 +1603,21 @@
         <v>29</v>
       </c>
       <c r="F26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1631,67 +1626,67 @@
         <v>29</v>
       </c>
       <c r="F27" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="G27" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="D28">
         <v>1</v>
       </c>
       <c r="E28" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29" t="s">
         <v>29</v>
-      </c>
-      <c r="F28" t="s">
-        <v>41</v>
-      </c>
-      <c r="G28" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>96</v>
-      </c>
-      <c r="B29" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" t="s">
-        <v>98</v>
-      </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-      <c r="E29" t="s">
-        <v>40</v>
       </c>
       <c r="F29" t="s">
         <v>12</v>
       </c>
       <c r="G29" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B30" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C30" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1703,18 +1698,18 @@
         <v>12</v>
       </c>
       <c r="G30" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C31" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1726,38 +1721,38 @@
         <v>12</v>
       </c>
       <c r="G31" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="D32">
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>29</v>
+        <v>111</v>
       </c>
       <c r="F32" t="s">
         <v>12</v>
       </c>
       <c r="G32" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B33" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C33" t="s">
         <v>10</v>
@@ -1766,159 +1761,159 @@
         <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>112</v>
+        <v>29</v>
       </c>
       <c r="F33" t="s">
         <v>12</v>
       </c>
       <c r="G33" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B34" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C34" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34" t="s">
+        <v>111</v>
+      </c>
+      <c r="F34" t="s">
+        <v>41</v>
+      </c>
+      <c r="G34" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>119</v>
+      </c>
+      <c r="B35" t="s">
+        <v>120</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35" t="s">
+        <v>81</v>
+      </c>
+      <c r="G35" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>122</v>
+      </c>
+      <c r="B36" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" t="s">
         <v>10</v>
       </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-      <c r="E34" t="s">
-        <v>29</v>
-      </c>
-      <c r="F34" t="s">
-        <v>12</v>
-      </c>
-      <c r="G34" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>117</v>
-      </c>
-      <c r="B35" t="s">
-        <v>118</v>
-      </c>
-      <c r="C35" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="E35" t="s">
-        <v>112</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36" t="s">
+        <v>111</v>
+      </c>
+      <c r="F36" t="s">
+        <v>81</v>
+      </c>
+      <c r="G36" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>125</v>
+      </c>
+      <c r="B37" t="s">
+        <v>126</v>
+      </c>
+      <c r="C37" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37" t="s">
+        <v>111</v>
+      </c>
+      <c r="F37" t="s">
         <v>41</v>
       </c>
-      <c r="G35" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>120</v>
-      </c>
-      <c r="B36" t="s">
-        <v>121</v>
-      </c>
-      <c r="C36" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="E36" t="s">
-        <v>29</v>
-      </c>
-      <c r="F36" t="s">
-        <v>82</v>
-      </c>
-      <c r="G36" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>123</v>
-      </c>
-      <c r="B37" t="s">
-        <v>124</v>
-      </c>
-      <c r="C37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-      <c r="E37" t="s">
-        <v>112</v>
-      </c>
-      <c r="F37" t="s">
-        <v>82</v>
-      </c>
       <c r="G37" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B38" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
+        <v>130</v>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F38" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="G38" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B39" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C39" t="s">
-        <v>131</v>
+        <v>19</v>
       </c>
       <c r="D39">
         <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="F39" t="s">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="G39" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B40" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C40" t="s">
         <v>19</v>
@@ -1927,21 +1922,21 @@
         <v>1</v>
       </c>
       <c r="E40" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="F40" t="s">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="G40" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C41" t="s">
         <v>19</v>
@@ -1950,59 +1945,13 @@
         <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F41" t="s">
         <v>41</v>
       </c>
       <c r="G41" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>140</v>
-      </c>
-      <c r="B42" t="s">
-        <v>141</v>
-      </c>
-      <c r="C42" t="s">
-        <v>19</v>
-      </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
-      <c r="E42" t="s">
-        <v>112</v>
-      </c>
-      <c r="F42" t="s">
-        <v>20</v>
-      </c>
-      <c r="G42" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>143</v>
-      </c>
-      <c r="B43" t="s">
         <v>144</v>
-      </c>
-      <c r="C43" t="s">
-        <v>19</v>
-      </c>
-      <c r="D43">
-        <v>1</v>
-      </c>
-      <c r="E43" t="s">
-        <v>112</v>
-      </c>
-      <c r="F43" t="s">
-        <v>41</v>
-      </c>
-      <c r="G43" t="s">
-        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2016,411 +1965,411 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:B86"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
     </row>
-    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="1"/>
+    </row>
+    <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="1"/>
-    </row>
-    <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
     </row>
-    <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>36</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>44</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="1" t="s">
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="1" t="s">
+      <c r="B24" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>160</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>77</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>157</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>161</v>
-      </c>
-      <c r="B30" s="1" t="s">
+    <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>78</v>
-      </c>
-      <c r="B36" s="1" t="s">
+    <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="1" t="s">
+    <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>75</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="1" t="s">
+    <row r="44" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="B44" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B44" s="1" t="s">
+    </row>
+    <row r="45" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
+      <c r="B48" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>130</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>131</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>66</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" t="s">
+    <row r="56" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>107</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="1" t="s">
+    <row r="59" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>97</v>
+      </c>
+      <c r="B64" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>175</v>
+      </c>
+      <c r="B66" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>177</v>
+      </c>
+      <c r="B70" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>179</v>
+      </c>
+      <c r="B74" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>181</v>
+      </c>
+      <c r="B78" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>184</v>
+      </c>
+      <c r="B84" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>108</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>98</v>
-      </c>
-      <c r="B64" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>176</v>
-      </c>
-      <c r="B66" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>178</v>
-      </c>
-      <c r="B70" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>180</v>
-      </c>
-      <c r="B74" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>182</v>
-      </c>
-      <c r="B78" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B79" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B81" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
+    <row r="86" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
         <v>185</v>
-      </c>
-      <c r="B84" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B85" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B86" t="s">
-        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -2434,21 +2383,21 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:G43"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
-    <col min="2" max="2" width="20.28515625" customWidth="1"/>
-    <col min="7" max="7" width="50.5703125" customWidth="1"/>
-    <col min="8" max="8" width="53.5703125" customWidth="1"/>
-    <col min="10" max="10" width="18.5703125" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="7" max="7" width="50.5546875" customWidth="1"/>
+    <col min="8" max="8" width="53.5546875" customWidth="1"/>
+    <col min="10" max="10" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2471,7 +2420,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2494,7 +2443,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -2517,12 +2466,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -2540,7 +2489,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -2563,7 +2512,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -2586,7 +2535,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -2609,7 +2558,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -2632,7 +2581,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -2655,12 +2604,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>
@@ -2675,10 +2624,10 @@
         <v>41</v>
       </c>
       <c r="G11" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -2701,12 +2650,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
@@ -2721,10 +2670,10 @@
         <v>47</v>
       </c>
       <c r="G13" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -2747,12 +2696,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C15" t="s">
         <v>19</v>
@@ -2767,15 +2716,15 @@
         <v>41</v>
       </c>
       <c r="G15" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>55</v>
       </c>
       <c r="B16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
@@ -2790,15 +2739,15 @@
         <v>41</v>
       </c>
       <c r="G16" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>58</v>
       </c>
       <c r="B17" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C17" t="s">
         <v>44</v>
@@ -2813,10 +2762,10 @@
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>61</v>
       </c>
@@ -2839,12 +2788,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C19" t="s">
         <v>66</v>
@@ -2862,12 +2811,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>67</v>
       </c>
       <c r="B20" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C20" t="s">
         <v>19</v>
@@ -2882,15 +2831,15 @@
         <v>41</v>
       </c>
       <c r="G20" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>70</v>
       </c>
       <c r="B21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C21" t="s">
         <v>10</v>
@@ -2905,18 +2854,18 @@
         <v>12</v>
       </c>
       <c r="G21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>73</v>
-      </c>
       <c r="B22" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D22">
         <v>2</v>
@@ -2931,15 +2880,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D23">
         <v>2</v>
@@ -2951,15 +2900,15 @@
         <v>12</v>
       </c>
       <c r="G23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>80</v>
-      </c>
       <c r="B24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C24" t="s">
         <v>16</v>
@@ -2971,18 +2920,18 @@
         <v>40</v>
       </c>
       <c r="F24" t="s">
+        <v>81</v>
+      </c>
+      <c r="G24" t="s">
         <v>82</v>
       </c>
-      <c r="G24" t="s">
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="B25" t="s">
         <v>84</v>
-      </c>
-      <c r="B25" t="s">
-        <v>85</v>
       </c>
       <c r="C25" t="s">
         <v>19</v>
@@ -2997,15 +2946,15 @@
         <v>41</v>
       </c>
       <c r="G25" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>87</v>
-      </c>
       <c r="B26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C26" t="s">
         <v>44</v>
@@ -3017,18 +2966,18 @@
         <v>29</v>
       </c>
       <c r="F26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" t="s">
         <v>206</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>90</v>
-      </c>
-      <c r="B27" t="s">
-        <v>207</v>
       </c>
       <c r="C27" t="s">
         <v>66</v>
@@ -3040,18 +2989,18 @@
         <v>29</v>
       </c>
       <c r="F27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G27" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
         <v>93</v>
-      </c>
-      <c r="B28" t="s">
-        <v>94</v>
       </c>
       <c r="C28" t="s">
         <v>19</v>
@@ -3066,18 +3015,18 @@
         <v>41</v>
       </c>
       <c r="G28" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>96</v>
-      </c>
       <c r="B29" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D29">
         <v>2</v>
@@ -3089,15 +3038,15 @@
         <v>12</v>
       </c>
       <c r="G29" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+      <c r="B30" t="s">
         <v>100</v>
-      </c>
-      <c r="B30" t="s">
-        <v>101</v>
       </c>
       <c r="C30" t="s">
         <v>19</v>
@@ -3112,15 +3061,15 @@
         <v>12</v>
       </c>
       <c r="G30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
         <v>103</v>
-      </c>
-      <c r="B31" t="s">
-        <v>104</v>
       </c>
       <c r="C31" t="s">
         <v>10</v>
@@ -3135,18 +3084,18 @@
         <v>12</v>
       </c>
       <c r="G31" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>106</v>
-      </c>
       <c r="B32" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D32">
         <v>2</v>
@@ -3158,15 +3107,15 @@
         <v>12</v>
       </c>
       <c r="G32" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>110</v>
-      </c>
       <c r="B33" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C33" t="s">
         <v>10</v>
@@ -3175,21 +3124,21 @@
         <v>2</v>
       </c>
       <c r="E33" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F33" t="s">
         <v>12</v>
       </c>
       <c r="G33" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>114</v>
-      </c>
       <c r="B34" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C34" t="s">
         <v>10</v>
@@ -3204,16 +3153,16 @@
         <v>12</v>
       </c>
       <c r="G34" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+      <c r="B35" t="s">
         <v>117</v>
       </c>
-      <c r="B35" t="s">
-        <v>118</v>
-      </c>
       <c r="C35" t="s">
         <v>19</v>
       </c>
@@ -3221,21 +3170,21 @@
         <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F35" t="s">
         <v>41</v>
       </c>
       <c r="G35" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>120</v>
-      </c>
       <c r="B36" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C36" t="s">
         <v>19</v>
@@ -3247,18 +3196,18 @@
         <v>29</v>
       </c>
       <c r="F36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G36" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>122</v>
+      </c>
+      <c r="B37" t="s">
         <v>123</v>
-      </c>
-      <c r="B37" t="s">
-        <v>124</v>
       </c>
       <c r="C37" t="s">
         <v>10</v>
@@ -3267,22 +3216,22 @@
         <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G37" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+      <c r="B38" t="s">
         <v>126</v>
       </c>
-      <c r="B38" t="s">
-        <v>127</v>
-      </c>
       <c r="C38" t="s">
         <v>19</v>
       </c>
@@ -3290,68 +3239,68 @@
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F38" t="s">
         <v>41</v>
       </c>
       <c r="G38" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+      <c r="B39" t="s">
         <v>129</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>130</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39" t="s">
+        <v>111</v>
+      </c>
+      <c r="F39" t="s">
+        <v>81</v>
+      </c>
+      <c r="G39" t="s">
         <v>131</v>
       </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="E39" t="s">
-        <v>112</v>
-      </c>
-      <c r="F39" t="s">
-        <v>82</v>
-      </c>
-      <c r="G39" t="s">
+    </row>
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+      <c r="B40" t="s">
         <v>133</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
         <v>134</v>
       </c>
-      <c r="C40" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>135</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>136</v>
       </c>
-      <c r="G40" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+      <c r="B41" t="s">
         <v>137</v>
       </c>
-      <c r="B41" t="s">
-        <v>138</v>
-      </c>
       <c r="C41" t="s">
         <v>19</v>
       </c>
@@ -3359,22 +3308,22 @@
         <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F41" t="s">
         <v>41</v>
       </c>
       <c r="G41" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+      <c r="B42" t="s">
         <v>140</v>
       </c>
-      <c r="B42" t="s">
-        <v>141</v>
-      </c>
       <c r="C42" t="s">
         <v>19</v>
       </c>
@@ -3382,22 +3331,22 @@
         <v>1</v>
       </c>
       <c r="E42" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F42" t="s">
         <v>20</v>
       </c>
       <c r="G42" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+      <c r="B43" t="s">
         <v>143</v>
       </c>
-      <c r="B43" t="s">
-        <v>144</v>
-      </c>
       <c r="C43" t="s">
         <v>19</v>
       </c>
@@ -3405,13 +3354,13 @@
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F43" t="s">
         <v>41</v>
       </c>
       <c r="G43" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -3422,146 +3371,146 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="96.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="96.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1" t="s">
         <v>214</v>
       </c>
-      <c r="B1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>217</v>
       </c>
-      <c r="B3" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
       <c r="B4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>220</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>222</v>
       </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>224</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>226</v>
       </c>
-      <c r="B8" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>228</v>
       </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>230</v>
       </c>
-      <c r="B10" t="s">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>232</v>
       </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>234</v>
       </c>
-      <c r="B12" t="s">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>236</v>
       </c>
-      <c r="B13" t="s">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>238</v>
       </c>
-      <c r="B14" t="s">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>240</v>
       </c>
-      <c r="B15" t="s">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>134</v>
-      </c>
-      <c r="B16" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
         <v>243</v>
-      </c>
-      <c r="B17" t="s">
-        <v>244</v>
       </c>
     </row>
   </sheetData>
